--- a/data/trans_dic/MCS12_SP_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49,36; 55,82</t>
+          <t>49,25; 55,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,13; 57,82</t>
+          <t>51,5; 57,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,63; 60,11</t>
+          <t>52,91; 59,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,6; 55,68</t>
+          <t>47,65; 55,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,32; 58,93</t>
+          <t>53,58; 58,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,5; 69,59</t>
+          <t>64,66; 69,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,52; 64,76</t>
+          <t>58,55; 65,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,27; 64,58</t>
+          <t>59,12; 64,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,39; 56,7</t>
+          <t>52,5; 56,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59,67; 64,06</t>
+          <t>59,54; 63,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57,17; 61,9</t>
+          <t>57,15; 61,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,47; 60,21</t>
+          <t>55,35; 60,11</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,51; 41,63</t>
+          <t>36,54; 41,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,98; 49,41</t>
+          <t>44,82; 49,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,59; 48,15</t>
+          <t>44,03; 48,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,0; 40,3</t>
+          <t>24,9; 40,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,31; 55,46</t>
+          <t>50,27; 55,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,32; 61,98</t>
+          <t>57,3; 62,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,27; 54,8</t>
+          <t>50,38; 54,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,17; 66,5</t>
+          <t>46,52; 65,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,04; 47,45</t>
+          <t>43,84; 47,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,34; 54,77</t>
+          <t>51,3; 54,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47,49; 50,79</t>
+          <t>47,66; 50,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,93; 51,44</t>
+          <t>37,52; 51,52</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,7; 43,19</t>
+          <t>35,15; 43,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,23; 50,31</t>
+          <t>40,15; 50,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,26; 48,91</t>
+          <t>40,59; 49,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,09; 45,6</t>
+          <t>36,99; 45,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,07; 57,29</t>
+          <t>48,61; 58,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,24; 59,27</t>
+          <t>49,46; 59,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,49; 55,2</t>
+          <t>46,11; 54,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,28; 51,31</t>
+          <t>44,4; 51,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,39; 49,08</t>
+          <t>42,56; 49,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,95; 53,07</t>
+          <t>46,28; 52,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44,33; 50,57</t>
+          <t>44,75; 50,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,72; 47,34</t>
+          <t>41,7; 46,99</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,41; 44,98</t>
+          <t>41,49; 45,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,12; 50,78</t>
+          <t>47,11; 50,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,19; 49,8</t>
+          <t>46,47; 49,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,24; 42,15</t>
+          <t>30,78; 42,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,47; 55,94</t>
+          <t>52,4; 56,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,2; 63,68</t>
+          <t>60,13; 63,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,12; 56,59</t>
+          <t>53,13; 56,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,29; 64,03</t>
+          <t>50,21; 61,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,59; 50,01</t>
+          <t>47,47; 49,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54,11; 56,65</t>
+          <t>54,33; 56,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50,27; 52,8</t>
+          <t>50,19; 52,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,97; 50,52</t>
+          <t>41,98; 51,34</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>509273; 575863</t>
+          <t>508133; 573687</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>498318; 563555</t>
+          <t>501943; 562188</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>396993; 453442</t>
+          <t>399093; 450819</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>242932; 284195</t>
+          <t>243203; 285505</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>701184; 775025</t>
+          <t>704699; 772229</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>862940; 930937</t>
+          <t>865034; 932512</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>582063; 644113</t>
+          <t>582358; 646744</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>441906; 481488</t>
+          <t>440774; 482626</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1229523; 1330650</t>
+          <t>1232126; 1328712</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1379826; 1481263</t>
+          <t>1376829; 1475856</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>999836; 1082553</t>
+          <t>999630; 1078301</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>696690; 756245</t>
+          <t>695166; 754936</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>618267; 704953</t>
+          <t>618829; 698643</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>883440; 970298</t>
+          <t>880203; 970981</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>905075; 999809</t>
+          <t>914134; 1003764</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>570385; 919412</t>
+          <t>567993; 917638</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>798710; 880509</t>
+          <t>798168; 878468</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1007612; 1089573</t>
+          <t>1007212; 1090524</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>999484; 1089548</t>
+          <t>1001695; 1086706</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1030592; 1484331</t>
+          <t>1038404; 1472903</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1445149; 1556880</t>
+          <t>1438529; 1556711</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1910661; 2038375</t>
+          <t>1909347; 2032774</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1930492; 2064432</t>
+          <t>1937096; 2062081</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1666873; 2321619</t>
+          <t>1693295; 2325306</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>191362; 238144</t>
+          <t>193844; 239729</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>193571; 242086</t>
+          <t>193191; 240648</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>220203; 267494</t>
+          <t>221958; 271145</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>239058; 293845</t>
+          <t>238358; 294590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>229027; 272946</t>
+          <t>231584; 276623</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>225852; 271832</t>
+          <t>226841; 271749</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>255310; 303102</t>
+          <t>253188; 300986</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>291164; 337387</t>
+          <t>291994; 336895</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>435663; 504473</t>
+          <t>437454; 505293</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>431856; 498733</t>
+          <t>434921; 495131</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>485914; 554259</t>
+          <t>490477; 558198</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>543189; 616426</t>
+          <t>542927; 611821</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1356877; 1473889</t>
+          <t>1359326; 1474346</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1611248; 1736600</t>
+          <t>1610904; 1730035</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1560023; 1682211</t>
+          <t>1569706; 1684356</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1004857; 1448320</t>
+          <t>1057783; 1452426</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1773088; 1890301</t>
+          <t>1770768; 1893868</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2139583; 2263492</t>
+          <t>2137010; 2255042</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1876160; 1998774</t>
+          <t>1876517; 2002321</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1828160; 2327713</t>
+          <t>1825405; 2245288</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3167492; 3328852</t>
+          <t>3159395; 3321312</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3773341; 3950958</t>
+          <t>3789296; 3961085</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3473358; 3648077</t>
+          <t>3468221; 3649275</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2968104; 3572404</t>
+          <t>2968782; 3630588</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/MCS12_SP_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49,25; 55,6</t>
+          <t>49,49; 55,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,5; 57,68</t>
+          <t>51,1; 57,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,91; 59,76</t>
+          <t>52,85; 60,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,65; 55,94</t>
+          <t>45,93; 54,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,58; 58,72</t>
+          <t>53,37; 58,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,66; 69,71</t>
+          <t>64,51; 69,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,55; 65,02</t>
+          <t>58,77; 64,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,12; 64,73</t>
+          <t>58,9; 64,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,5; 56,62</t>
+          <t>52,37; 56,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59,54; 63,82</t>
+          <t>59,67; 63,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57,15; 61,65</t>
+          <t>57,01; 61,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,35; 60,11</t>
+          <t>54,53; 59,07</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,54; 41,26</t>
+          <t>36,45; 41,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,82; 49,44</t>
+          <t>44,9; 49,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,03; 48,34</t>
+          <t>43,95; 48,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,9; 40,22</t>
+          <t>37,94; 42,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,27; 55,33</t>
+          <t>50,38; 55,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,3; 62,04</t>
+          <t>57,21; 61,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,38; 54,66</t>
+          <t>50,5; 54,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,52; 65,99</t>
+          <t>45,21; 49,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,84; 47,44</t>
+          <t>43,94; 47,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,3; 54,62</t>
+          <t>51,29; 54,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47,66; 50,73</t>
+          <t>47,4; 50,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,52; 51,52</t>
+          <t>41,86; 45,01</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,15; 43,48</t>
+          <t>35,21; 43,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,15; 50,01</t>
+          <t>39,9; 49,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,59; 49,58</t>
+          <t>40,0; 49,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,99; 45,71</t>
+          <t>37,03; 45,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,61; 58,06</t>
+          <t>48,9; 58,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,46; 59,25</t>
+          <t>49,71; 59,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,11; 54,81</t>
+          <t>46,47; 55,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,4; 51,23</t>
+          <t>45,72; 52,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,56; 49,16</t>
+          <t>42,62; 49,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,28; 52,68</t>
+          <t>45,86; 53,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44,75; 50,93</t>
+          <t>44,64; 50,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,7; 46,99</t>
+          <t>42,76; 47,83</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,49; 45,0</t>
+          <t>41,5; 44,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,11; 50,59</t>
+          <t>47,13; 50,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,47; 49,87</t>
+          <t>46,36; 49,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,78; 42,27</t>
+          <t>40,08; 43,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,4; 56,04</t>
+          <t>52,49; 55,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,13; 63,45</t>
+          <t>60,06; 63,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,13; 56,69</t>
+          <t>53,04; 56,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,21; 61,76</t>
+          <t>49,24; 52,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,47; 49,9</t>
+          <t>47,5; 49,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54,33; 56,8</t>
+          <t>54,15; 56,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50,19; 52,81</t>
+          <t>50,36; 52,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,98; 51,34</t>
+          <t>45,4; 47,76</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264622</t>
+          <t>285741</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>461719</t>
+          <t>501677</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>726340</t>
+          <t>787418</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>508133; 573687</t>
+          <t>510560; 576629</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>501943; 562188</t>
+          <t>498068; 561517</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399093; 450819</t>
+          <t>398683; 452735</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>243203; 285505</t>
+          <t>263446; 309794</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>704699; 772229</t>
+          <t>701889; 771943</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>865034; 932512</t>
+          <t>863015; 932865</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>582358; 646744</t>
+          <t>584585; 645433</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>440774; 482626</t>
+          <t>477971; 522659</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1232126; 1328712</t>
+          <t>1229144; 1326962</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1376829; 1475856</t>
+          <t>1379765; 1478736</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>999630; 1078301</t>
+          <t>997113; 1080939</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>695166; 754936</t>
+          <t>755318; 818179</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>798879</t>
+          <t>887951</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1182106</t>
+          <t>1023723</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1980985</t>
+          <t>1911674</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>618829; 698643</t>
+          <t>617200; 697461</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>880203; 970981</t>
+          <t>881914; 969725</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>914134; 1003764</t>
+          <t>912581; 1006467</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>567993; 917638</t>
+          <t>842746; 943079</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>798168; 878468</t>
+          <t>799854; 879269</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1007212; 1090524</t>
+          <t>1005668; 1086176</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1001695; 1086706</t>
+          <t>1004104; 1091454</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1038404; 1472903</t>
+          <t>978892; 1069441</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1438529; 1556711</t>
+          <t>1441821; 1554370</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1909347; 2032774</t>
+          <t>1908983; 2039437</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1937096; 2062081</t>
+          <t>1926606; 2060254</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1693295; 2325306</t>
+          <t>1836014; 1974369</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>264832</t>
+          <t>293152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>314279</t>
+          <t>358254</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>579112</t>
+          <t>651407</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>193844; 239729</t>
+          <t>194137; 241770</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>193191; 240648</t>
+          <t>191988; 238103</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>221958; 271145</t>
+          <t>218777; 269192</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>238358; 294590</t>
+          <t>262586; 319102</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>231584; 276623</t>
+          <t>232965; 277642</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>226841; 271749</t>
+          <t>228005; 272037</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>253188; 300986</t>
+          <t>255203; 302218</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>291994; 336895</t>
+          <t>334584; 381363</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>437454; 505293</t>
+          <t>438106; 504932</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>434921; 495131</t>
+          <t>430970; 499930</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>490477; 558198</t>
+          <t>489250; 555107</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>542927; 611821</t>
+          <t>616201; 689131</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1328333</t>
+          <t>1466845</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1958104</t>
+          <t>1883653</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3286436</t>
+          <t>3350498</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1359326; 1474346</t>
+          <t>1359732; 1472819</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1610904; 1730035</t>
+          <t>1611880; 1733851</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1569706; 1684356</t>
+          <t>1565764; 1683443</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1057783; 1452426</t>
+          <t>1404371; 1528960</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1770768; 1893868</t>
+          <t>1773654; 1890895</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2137010; 2255042</t>
+          <t>2134713; 2261141</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1876517; 2002321</t>
+          <t>1873580; 1997096</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1825405; 2245288</t>
+          <t>1826009; 1937038</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3159395; 3321312</t>
+          <t>3161364; 3326987</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3789296; 3961085</t>
+          <t>3776659; 3954011</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3468221; 3649275</t>
+          <t>3479820; 3648160</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2968782; 3630588</t>
+          <t>3274349; 3444789</t>
         </is>
       </c>
     </row>
